--- a/Data/PAM_CBLS_Aquarium.xlsx
+++ b/Data/PAM_CBLS_Aquarium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PUTNAM LAB\CBLS_Wetlab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D899D2-838E-4914-85E7-90CE7C417494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35360A62-0E8D-4B24-B0C5-0E0F12B5C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -132,92 +132,48 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF0000FF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,991 +455,962 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>46086</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="5">
         <v>0.5</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="13">
-        <v>30</v>
-      </c>
-      <c r="G2" s="13">
+      <c r="E2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="7">
+        <v>30</v>
+      </c>
+      <c r="G2" s="7">
         <v>3887</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="7">
         <v>304</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="7">
         <v>938</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="7">
         <v>690</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="7">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>46086</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="5">
         <v>0.5</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="13">
-        <v>30</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="E3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="7">
+        <v>30</v>
+      </c>
+      <c r="G3" s="7">
         <v>3888</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="7">
         <v>280</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="7">
         <v>908</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="7">
         <v>691</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="7">
         <v>6.9099999999999995E-2</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>46086</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="5">
         <v>0.5</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="13">
-        <v>30</v>
-      </c>
-      <c r="G4" s="13">
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7">
+        <v>30</v>
+      </c>
+      <c r="G4" s="7">
         <v>3890</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="7">
         <v>415</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="7">
         <v>1360</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="7">
         <v>694</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="7">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>46086</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="5">
         <v>0.5</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="13">
-        <v>30</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7">
+        <v>30</v>
+      </c>
+      <c r="G5" s="7">
         <v>3891</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="7">
         <v>376</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="7">
         <v>1223</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="7">
         <v>692</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="7">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>46086</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="5">
         <v>0.5</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="13">
-        <v>30</v>
-      </c>
-      <c r="G6" s="13">
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="7">
+        <v>30</v>
+      </c>
+      <c r="G6" s="7">
         <v>3892</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="7">
         <v>305</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="7">
         <v>981</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="7">
         <v>689</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="7">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>46086</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="5">
         <v>0.5</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13">
-        <v>30</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="E7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="7">
+        <v>30</v>
+      </c>
+      <c r="G7" s="7">
         <v>3894</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="7">
         <v>281</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="7">
         <v>921</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="7">
         <v>694</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="7">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="W7" s="7"/>
-    </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>46086</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="5">
         <v>0.5</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="17">
-        <v>30</v>
-      </c>
-      <c r="G8" s="17">
+      <c r="E8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="7">
+        <v>30</v>
+      </c>
+      <c r="G8" s="7">
         <v>3895</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="7">
         <v>292</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="7">
         <v>978</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="7">
         <v>701</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="7">
         <v>7.0099999999999996E-2</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="4">
-        <v>30</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="C9" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="13">
+        <v>30</v>
+      </c>
+      <c r="G9" s="13">
         <v>3897</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="13">
         <v>309</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="13">
         <v>1033</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="13">
         <v>700</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="4">
-        <v>30</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="C10" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="13">
+        <v>30</v>
+      </c>
+      <c r="G10" s="13">
         <v>3898</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="13">
         <v>399</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="13">
         <v>1201</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="13">
         <v>667</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="13">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4">
-        <v>30</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="C11" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="13">
+        <v>30</v>
+      </c>
+      <c r="G11" s="13">
         <v>3899</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="13">
         <v>430</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="13">
         <v>1275</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="13">
         <v>662</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="13">
         <v>6.6199999999999995E-2</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="4">
-        <v>30</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="C12" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="13">
+        <v>30</v>
+      </c>
+      <c r="G12" s="13">
         <v>3900</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="13">
         <v>283</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="13">
         <v>904</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="13">
         <v>686</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="13">
         <v>6.8599999999999994E-2</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="4">
-        <v>30</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="13">
+        <v>30</v>
+      </c>
+      <c r="G13" s="13">
         <v>3902</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="13">
         <v>702</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="13">
         <v>1484</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="13">
         <v>526</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="13">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="C14" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="4">
-        <v>30</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="F14" s="13">
+        <v>30</v>
+      </c>
+      <c r="G14" s="13">
         <v>3903</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="13">
         <v>521</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="13">
         <v>1401</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="13">
         <v>628</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="13">
         <v>6.2799999999999995E-2</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="C15" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="4">
-        <v>30</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="F15" s="13">
+        <v>30</v>
+      </c>
+      <c r="G15" s="13">
         <v>3904</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="13">
         <v>401</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="13">
         <v>897</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="13">
         <v>552</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="13">
         <v>5.5199999999999999E-2</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="C16" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="4">
-        <v>30</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="F16" s="13">
+        <v>30</v>
+      </c>
+      <c r="G16" s="13">
         <v>3905</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="13">
         <v>348</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="13">
         <v>1376</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="13">
         <v>747</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="13">
         <v>7.4700000000000003E-2</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="C17" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="4">
-        <v>30</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="F17" s="13">
+        <v>30</v>
+      </c>
+      <c r="G17" s="13">
         <v>3906</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="13">
         <v>530</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="13">
         <v>1629</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="13">
         <v>674</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="13">
         <v>6.7400000000000002E-2</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="C18" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="4">
-        <v>30</v>
-      </c>
-      <c r="G18" s="4">
+      <c r="F18" s="13">
+        <v>30</v>
+      </c>
+      <c r="G18" s="13">
         <v>3907</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="13">
         <v>509</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="13">
         <v>1629</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="13">
         <v>687</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="13">
         <v>6.8699999999999997E-2</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="4">
-        <v>30</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="C19" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="13">
+        <v>30</v>
+      </c>
+      <c r="G19" s="13">
         <v>3909</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="13">
         <v>325</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="13">
         <v>1044</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="13">
         <v>688</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="13">
         <v>6.88E-2</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="4">
-        <v>30</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="C20" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="13">
+        <v>30</v>
+      </c>
+      <c r="G20" s="13">
         <v>3910</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="13">
         <v>321</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="13">
         <v>833</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="13">
         <v>614</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="13">
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="L20" s="2"/>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="4">
-        <v>30</v>
-      </c>
-      <c r="G21" s="4">
+      <c r="C21" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="13">
+        <v>30</v>
+      </c>
+      <c r="G21" s="13">
         <v>3911</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="13">
         <v>337</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="13">
         <v>1027</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="13">
         <v>671</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="13">
         <v>6.7100000000000007E-2</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="4">
-        <v>30</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="C22" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="13">
+        <v>30</v>
+      </c>
+      <c r="G22" s="13">
         <v>3912</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="13">
         <v>589</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="13">
         <v>1896</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="13">
         <v>689</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="13">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="L22" s="2"/>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="4">
-        <v>30</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="C23" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="13">
+        <v>30</v>
+      </c>
+      <c r="G23" s="13">
         <v>3913</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="13">
         <v>362</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="13">
         <v>1105</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="13">
         <v>672</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="13">
         <v>6.7199999999999996E-2</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="3">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="4">
-        <v>30</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="C24" s="11">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="13">
+        <v>30</v>
+      </c>
+      <c r="G24" s="13">
         <v>3914</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="13">
         <v>332</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="13">
         <v>991</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="13">
         <v>664</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="13">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/PAM_CBLS_Aquarium.xlsx
+++ b/Data/PAM_CBLS_Aquarium.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PUTNAM LAB\CBLS_Wetlab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35360A62-0E8D-4B24-B0C5-0E0F12B5C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524593EF-18FC-4770-8838-16B3D54E182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>MM;JH</t>
+  </si>
+  <si>
+    <t>Timepoint</t>
   </si>
 </sst>
 </file>
@@ -136,43 +139,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -455,89 +457,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D2" s="4">
         <v>0.5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="7">
-        <v>30</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6">
+        <v>30</v>
+      </c>
+      <c r="H2" s="6">
         <v>3887</v>
       </c>
-      <c r="H2" s="7">
+      <c r="I2" s="6">
         <v>304</v>
       </c>
-      <c r="I2" s="7">
+      <c r="J2" s="6">
         <v>938</v>
       </c>
-      <c r="J2" s="7">
+      <c r="K2" s="6">
         <v>690</v>
       </c>
-      <c r="K2" s="7">
+      <c r="L2" s="6">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -545,45 +552,48 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D3" s="4">
         <v>0.5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="7">
-        <v>30</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6">
+        <v>30</v>
+      </c>
+      <c r="H3" s="6">
         <v>3888</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I3" s="6">
         <v>280</v>
       </c>
-      <c r="I3" s="7">
+      <c r="J3" s="6">
         <v>908</v>
       </c>
-      <c r="J3" s="7">
+      <c r="K3" s="6">
         <v>691</v>
       </c>
-      <c r="K3" s="7">
+      <c r="L3" s="6">
         <v>6.9099999999999995E-2</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -591,45 +601,48 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7">
-        <v>30</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="6">
+        <v>30</v>
+      </c>
+      <c r="H4" s="6">
         <v>3890</v>
       </c>
-      <c r="H4" s="7">
+      <c r="I4" s="6">
         <v>415</v>
       </c>
-      <c r="I4" s="7">
+      <c r="J4" s="6">
         <v>1360</v>
       </c>
-      <c r="J4" s="7">
+      <c r="K4" s="6">
         <v>694</v>
       </c>
-      <c r="K4" s="7">
+      <c r="L4" s="6">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -637,45 +650,48 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="7">
-        <v>30</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="6">
+        <v>30</v>
+      </c>
+      <c r="H5" s="6">
         <v>3891</v>
       </c>
-      <c r="H5" s="7">
+      <c r="I5" s="6">
         <v>376</v>
       </c>
-      <c r="I5" s="7">
+      <c r="J5" s="6">
         <v>1223</v>
       </c>
-      <c r="J5" s="7">
+      <c r="K5" s="6">
         <v>692</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="6">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -683,45 +699,48 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D6" s="4">
         <v>0.5</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="7">
-        <v>30</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="6">
+        <v>30</v>
+      </c>
+      <c r="H6" s="6">
         <v>3892</v>
       </c>
-      <c r="H6" s="7">
+      <c r="I6" s="6">
         <v>305</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="6">
         <v>981</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="6">
         <v>689</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="6">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -729,45 +748,48 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D7" s="4">
         <v>0.5</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7">
-        <v>30</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="F7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6">
         <v>3894</v>
       </c>
-      <c r="H7" s="7">
+      <c r="I7" s="6">
         <v>281</v>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="6">
         <v>921</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="6">
         <v>694</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="6">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -775,45 +797,48 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="2">
+        <v>20260305</v>
+      </c>
+      <c r="D8" s="4">
         <v>0.5</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7">
-        <v>30</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="F8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="6">
+        <v>30</v>
+      </c>
+      <c r="H8" s="6">
         <v>3895</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I8" s="6">
         <v>292</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="6">
         <v>978</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="6">
         <v>701</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="6">
         <v>7.0099999999999996E-2</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -821,596 +846,645 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="13">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="C9" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="12">
+        <v>30</v>
+      </c>
+      <c r="H9" s="12">
         <v>3897</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="12">
         <v>309</v>
       </c>
-      <c r="I9" s="13">
+      <c r="J9" s="12">
         <v>1033</v>
       </c>
-      <c r="J9" s="13">
+      <c r="K9" s="12">
         <v>700</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="13">
-        <v>30</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="C10" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="12">
+        <v>30</v>
+      </c>
+      <c r="H10" s="12">
         <v>3898</v>
       </c>
-      <c r="H10" s="13">
+      <c r="I10" s="12">
         <v>399</v>
       </c>
-      <c r="I10" s="13">
+      <c r="J10" s="12">
         <v>1201</v>
       </c>
-      <c r="J10" s="13">
+      <c r="K10" s="12">
         <v>667</v>
       </c>
-      <c r="K10" s="13">
+      <c r="L10" s="12">
         <v>6.6699999999999995E-2</v>
       </c>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="13">
-        <v>30</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="C11" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="12">
+        <v>30</v>
+      </c>
+      <c r="H11" s="12">
         <v>3899</v>
       </c>
-      <c r="H11" s="13">
+      <c r="I11" s="12">
         <v>430</v>
       </c>
-      <c r="I11" s="13">
+      <c r="J11" s="12">
         <v>1275</v>
       </c>
-      <c r="J11" s="13">
+      <c r="K11" s="12">
         <v>662</v>
       </c>
-      <c r="K11" s="13">
+      <c r="L11" s="12">
         <v>6.6199999999999995E-2</v>
       </c>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="M11" s="9"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="13">
-        <v>30</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="C12" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="12">
+        <v>30</v>
+      </c>
+      <c r="H12" s="12">
         <v>3900</v>
       </c>
-      <c r="H12" s="13">
+      <c r="I12" s="12">
         <v>283</v>
       </c>
-      <c r="I12" s="13">
+      <c r="J12" s="12">
         <v>904</v>
       </c>
-      <c r="J12" s="13">
+      <c r="K12" s="12">
         <v>686</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="12">
         <v>6.8599999999999994E-2</v>
       </c>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="C13" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="13">
-        <v>30</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
+        <v>30</v>
+      </c>
+      <c r="H13" s="12">
         <v>3902</v>
       </c>
-      <c r="H13" s="13">
+      <c r="I13" s="12">
         <v>702</v>
       </c>
-      <c r="I13" s="13">
+      <c r="J13" s="12">
         <v>1484</v>
       </c>
-      <c r="J13" s="13">
+      <c r="K13" s="12">
         <v>526</v>
       </c>
-      <c r="K13" s="13">
+      <c r="L13" s="12">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="M13" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="C14" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="13">
-        <v>30</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
+        <v>30</v>
+      </c>
+      <c r="H14" s="12">
         <v>3903</v>
       </c>
-      <c r="H14" s="13">
+      <c r="I14" s="12">
         <v>521</v>
       </c>
-      <c r="I14" s="13">
+      <c r="J14" s="12">
         <v>1401</v>
       </c>
-      <c r="J14" s="13">
+      <c r="K14" s="12">
         <v>628</v>
       </c>
-      <c r="K14" s="13">
+      <c r="L14" s="12">
         <v>6.2799999999999995E-2</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B15" s="10" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="12" t="s">
+      <c r="C15" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="13">
-        <v>30</v>
-      </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
+        <v>30</v>
+      </c>
+      <c r="H15" s="12">
         <v>3904</v>
       </c>
-      <c r="H15" s="13">
+      <c r="I15" s="12">
         <v>401</v>
       </c>
-      <c r="I15" s="13">
+      <c r="J15" s="12">
         <v>897</v>
       </c>
-      <c r="J15" s="13">
+      <c r="K15" s="12">
         <v>552</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="12">
         <v>5.5199999999999999E-2</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="M15" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B16" s="10" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="12" t="s">
+      <c r="C16" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="13">
-        <v>30</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
+        <v>30</v>
+      </c>
+      <c r="H16" s="12">
         <v>3905</v>
       </c>
-      <c r="H16" s="13">
+      <c r="I16" s="12">
         <v>348</v>
       </c>
-      <c r="I16" s="13">
+      <c r="J16" s="12">
         <v>1376</v>
       </c>
-      <c r="J16" s="13">
+      <c r="K16" s="12">
         <v>747</v>
       </c>
-      <c r="K16" s="13">
+      <c r="L16" s="12">
         <v>7.4700000000000003E-2</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="M16" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="C17" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="13">
-        <v>30</v>
-      </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
+        <v>30</v>
+      </c>
+      <c r="H17" s="12">
         <v>3906</v>
       </c>
-      <c r="H17" s="13">
+      <c r="I17" s="12">
         <v>530</v>
       </c>
-      <c r="I17" s="13">
+      <c r="J17" s="12">
         <v>1629</v>
       </c>
-      <c r="J17" s="13">
+      <c r="K17" s="12">
         <v>674</v>
       </c>
-      <c r="K17" s="13">
+      <c r="L17" s="12">
         <v>6.7400000000000002E-2</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B18" s="10" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="12" t="s">
+      <c r="C18" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="13">
-        <v>30</v>
-      </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
+        <v>30</v>
+      </c>
+      <c r="H18" s="12">
         <v>3907</v>
       </c>
-      <c r="H18" s="13">
+      <c r="I18" s="12">
         <v>509</v>
       </c>
-      <c r="I18" s="13">
+      <c r="J18" s="12">
         <v>1629</v>
       </c>
-      <c r="J18" s="13">
+      <c r="K18" s="12">
         <v>687</v>
       </c>
-      <c r="K18" s="13">
+      <c r="L18" s="12">
         <v>6.8699999999999997E-2</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="M18" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="13">
-        <v>30</v>
-      </c>
-      <c r="G19" s="13">
+      <c r="C19" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="12">
+        <v>30</v>
+      </c>
+      <c r="H19" s="12">
         <v>3909</v>
       </c>
-      <c r="H19" s="13">
+      <c r="I19" s="12">
         <v>325</v>
       </c>
-      <c r="I19" s="13">
+      <c r="J19" s="12">
         <v>1044</v>
       </c>
-      <c r="J19" s="13">
+      <c r="K19" s="12">
         <v>688</v>
       </c>
-      <c r="K19" s="13">
+      <c r="L19" s="12">
         <v>6.88E-2</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="M19" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B20" s="10" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="13">
-        <v>30</v>
-      </c>
-      <c r="G20" s="13">
+      <c r="C20" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="12">
+        <v>30</v>
+      </c>
+      <c r="H20" s="12">
         <v>3910</v>
       </c>
-      <c r="H20" s="13">
+      <c r="I20" s="12">
         <v>321</v>
       </c>
-      <c r="I20" s="13">
+      <c r="J20" s="12">
         <v>833</v>
       </c>
-      <c r="J20" s="13">
+      <c r="K20" s="12">
         <v>614</v>
       </c>
-      <c r="K20" s="13">
+      <c r="L20" s="12">
         <v>6.1400000000000003E-2</v>
       </c>
-      <c r="L20" s="10"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B21" s="10" t="s">
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="13">
-        <v>30</v>
-      </c>
-      <c r="G21" s="13">
+      <c r="C21" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="12">
+        <v>30</v>
+      </c>
+      <c r="H21" s="12">
         <v>3911</v>
       </c>
-      <c r="H21" s="13">
+      <c r="I21" s="12">
         <v>337</v>
       </c>
-      <c r="I21" s="13">
+      <c r="J21" s="12">
         <v>1027</v>
       </c>
-      <c r="J21" s="13">
+      <c r="K21" s="12">
         <v>671</v>
       </c>
-      <c r="K21" s="13">
+      <c r="L21" s="12">
         <v>6.7100000000000007E-2</v>
       </c>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="M21" s="9"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="13">
-        <v>30</v>
-      </c>
-      <c r="G22" s="13">
+      <c r="C22" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="12">
+        <v>30</v>
+      </c>
+      <c r="H22" s="12">
         <v>3912</v>
       </c>
-      <c r="H22" s="13">
+      <c r="I22" s="12">
         <v>589</v>
       </c>
-      <c r="I22" s="13">
+      <c r="J22" s="12">
         <v>1896</v>
       </c>
-      <c r="J22" s="13">
+      <c r="K22" s="12">
         <v>689</v>
       </c>
-      <c r="K22" s="13">
+      <c r="L22" s="12">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="M22" s="9"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="13">
-        <v>30</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="C23" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="12">
+        <v>30</v>
+      </c>
+      <c r="H23" s="12">
         <v>3913</v>
       </c>
-      <c r="H23" s="13">
+      <c r="I23" s="12">
         <v>362</v>
       </c>
-      <c r="I23" s="13">
+      <c r="J23" s="12">
         <v>1105</v>
       </c>
-      <c r="J23" s="13">
+      <c r="K23" s="12">
         <v>672</v>
       </c>
-      <c r="K23" s="13">
+      <c r="L23" s="12">
         <v>6.7199999999999996E-2</v>
       </c>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>46091</v>
-      </c>
-      <c r="B24" s="10" t="s">
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="11">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="13">
-        <v>30</v>
-      </c>
-      <c r="G24" s="13">
+      <c r="C24" s="8">
+        <v>20260310</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="12">
+        <v>30</v>
+      </c>
+      <c r="H24" s="12">
         <v>3914</v>
       </c>
-      <c r="H24" s="13">
+      <c r="I24" s="12">
         <v>332</v>
       </c>
-      <c r="I24" s="13">
+      <c r="J24" s="12">
         <v>991</v>
       </c>
-      <c r="J24" s="13">
+      <c r="K24" s="12">
         <v>664</v>
       </c>
-      <c r="K24" s="13">
+      <c r="L24" s="12">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="L24" s="10"/>
+      <c r="M24" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
